--- a/Documents/devfiles/excel/DevoloperActivities.xlsx
+++ b/Documents/devfiles/excel/DevoloperActivities.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\devfiles\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gitlab\joboffer\Documents\devfiles\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CA5BE6-ECE1-4EEC-AC32-76B91BF5A623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BC441A-4112-48F2-8A9A-0DDB48FFF0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{337275F3-F812-418C-B02B-6398BC7C9B39}"/>
+    <workbookView xWindow="-25260" yWindow="5445" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{337275F3-F812-418C-B02B-6398BC7C9B39}"/>
   </bookViews>
   <sheets>
     <sheet name="Draft" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="116">
   <si>
     <t>Daily sync of responses from MS forms to be scheduled at: 7AM, 12NN, 3PM</t>
   </si>
@@ -383,6 +383,24 @@
   </si>
   <si>
     <t>new password - hrodooffer@1</t>
+  </si>
+  <si>
+    <t>Manual Upload</t>
+  </si>
+  <si>
+    <t>Export</t>
+  </si>
+  <si>
+    <t>Remove Email Addres</t>
+  </si>
+  <si>
+    <t>Label "Dbox Sync"</t>
+  </si>
+  <si>
+    <t>Import Excel</t>
+  </si>
+  <si>
+    <t>Last Sync Date Time</t>
   </si>
 </sst>
 </file>
@@ -886,25 +904,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B9038A7-AD59-482A-8671-D3CB2D87EC41}">
   <dimension ref="B2:O8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" customWidth="1"/>
-    <col min="4" max="4" width="34.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" customWidth="1"/>
+    <col min="4" max="4" width="34.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.1796875" customWidth="1"/>
-    <col min="8" max="8" width="37.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.21875" customWidth="1"/>
+    <col min="8" max="8" width="37.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" customWidth="1"/>
     <col min="11" max="11" width="23" customWidth="1"/>
-    <col min="12" max="12" width="20.36328125" customWidth="1"/>
-    <col min="13" max="13" width="19.453125" customWidth="1"/>
-    <col min="14" max="14" width="28.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.33203125" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" customWidth="1"/>
+    <col min="14" max="14" width="28.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
@@ -948,7 +966,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -992,7 +1010,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1021,7 +1039,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1041,7 +1059,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -1052,12 +1070,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>49</v>
       </c>
@@ -1070,29 +1088,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED69CB7-7627-4EC8-B1DF-810A0B37AA79}">
   <dimension ref="C1:Y26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" customWidth="1"/>
-    <col min="3" max="3" width="62.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="63.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="63.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.90625" customWidth="1"/>
-    <col min="11" max="11" width="55.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="46.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="90.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="57.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="32.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" customWidth="1"/>
+    <col min="3" max="3" width="66.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="63.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="63.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.88671875" customWidth="1"/>
+    <col min="11" max="11" width="55.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="46.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="90.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="57.21875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="32.109375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="33" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="31.6328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="31.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="3:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C1" s="7">
         <v>46274</v>
       </c>
@@ -1163,7 +1181,7 @@
         <v>46296</v>
       </c>
     </row>
-    <row r="2" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1216,7 +1234,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>7</v>
       </c>
@@ -1251,7 +1269,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>8</v>
       </c>
@@ -1286,7 +1304,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>6</v>
       </c>
@@ -1324,7 +1342,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>0</v>
       </c>
@@ -1344,10 +1362,13 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>1</v>
       </c>
+      <c r="D7" t="s">
+        <v>110</v>
+      </c>
       <c r="E7" t="s">
         <v>61</v>
       </c>
@@ -1373,7 +1394,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>111</v>
+      </c>
       <c r="I8" t="s">
         <v>22</v>
       </c>
@@ -1390,7 +1414,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
       <c r="E9" t="s">
         <v>72</v>
       </c>
@@ -1406,8 +1433,14 @@
       <c r="O9" s="11" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="10" spans="3:25" x14ac:dyDescent="0.35">
+      <c r="Q9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>113</v>
+      </c>
       <c r="E10" s="11" t="s">
         <v>73</v>
       </c>
@@ -1423,8 +1456,11 @@
       <c r="O10" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="11" spans="3:25" x14ac:dyDescent="0.35">
+      <c r="Q10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="3:25" x14ac:dyDescent="0.3">
       <c r="I11" t="s">
         <v>24</v>
       </c>
@@ -1434,8 +1470,11 @@
       <c r="O11" s="11" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="12" spans="3:25" x14ac:dyDescent="0.35">
+      <c r="Q11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="3:25" x14ac:dyDescent="0.3">
       <c r="E12" t="s">
         <v>74</v>
       </c>
@@ -1446,7 +1485,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:25" x14ac:dyDescent="0.3">
       <c r="E13" t="s">
         <v>75</v>
       </c>
@@ -1457,7 +1496,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:25" x14ac:dyDescent="0.3">
       <c r="E14" s="11" t="s">
         <v>76</v>
       </c>
@@ -1465,7 +1504,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:25" x14ac:dyDescent="0.3">
       <c r="E15" s="11" t="s">
         <v>77</v>
       </c>
@@ -1473,7 +1512,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:25" x14ac:dyDescent="0.3">
       <c r="E16" s="11" t="s">
         <v>78</v>
       </c>
@@ -1484,7 +1523,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="5:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="5:9" x14ac:dyDescent="0.3">
       <c r="E17" s="11" t="s">
         <v>79</v>
       </c>
@@ -1492,7 +1531,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="5:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="5:9" x14ac:dyDescent="0.3">
       <c r="H18" t="s">
         <v>81</v>
       </c>
@@ -1500,7 +1539,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="5:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="5:9" x14ac:dyDescent="0.3">
       <c r="H19" s="11" t="s">
         <v>82</v>
       </c>
@@ -1508,7 +1547,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="5:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="5:9" x14ac:dyDescent="0.3">
       <c r="H20" s="11" t="s">
         <v>83</v>
       </c>
@@ -1516,7 +1555,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="5:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="5:9" x14ac:dyDescent="0.3">
       <c r="H21" s="11" t="s">
         <v>84</v>
       </c>
@@ -1524,17 +1563,17 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="5:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="5:9" x14ac:dyDescent="0.3">
       <c r="I23" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="5:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="5:9" x14ac:dyDescent="0.3">
       <c r="I24" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="26" spans="5:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="5:9" x14ac:dyDescent="0.3">
       <c r="I26" t="s">
         <v>95</v>
       </c>
@@ -1547,52 +1586,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B8C298-1B1E-4BB2-871B-BB0A034CE40B}">
   <dimension ref="B2:B14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="123.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="123.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" s="14" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="15" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="14" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>109</v>
       </c>

--- a/Documents/devfiles/excel/DevoloperActivities.xlsx
+++ b/Documents/devfiles/excel/DevoloperActivities.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gitlab\joboffer\Documents\devfiles\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\devfiles\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BC441A-4112-48F2-8A9A-0DDB48FFF0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CEDFCD-1AB9-44E1-8196-BDDCF2D0366F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25260" yWindow="5445" windowWidth="23040" windowHeight="12120" activeTab="1" xr2:uid="{337275F3-F812-418C-B02B-6398BC7C9B39}"/>
+    <workbookView xWindow="290" yWindow="860" windowWidth="19000" windowHeight="10510" activeTab="1" xr2:uid="{337275F3-F812-418C-B02B-6398BC7C9B39}"/>
   </bookViews>
   <sheets>
     <sheet name="Draft" sheetId="2" r:id="rId1"/>
     <sheet name="Daily Task" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="160">
   <si>
     <t>Daily sync of responses from MS forms to be scheduled at: 7AM, 12NN, 3PM</t>
   </si>
@@ -401,6 +402,138 @@
   </si>
   <si>
     <t>Last Sync Date Time</t>
+  </si>
+  <si>
+    <t>Week 1</t>
+  </si>
+  <si>
+    <t>Date of Completion</t>
+  </si>
+  <si>
+    <t>Tool Config:</t>
+  </si>
+  <si>
+    <t>1. Sync of MSForms and Dbox.</t>
+  </si>
+  <si>
+    <t>2. Include details Last Sync Date and Time for DBOX and MSForms</t>
+  </si>
+  <si>
+    <t>Save analysis must be open on any status.</t>
+  </si>
+  <si>
+    <t>Add Candidate Remarks from MS Form in the OPTION Table</t>
+  </si>
+  <si>
+    <t>Ajust configuration on approval matrix, BEYON (above compa ratio) can still be submitted and elevated to PRESIDENT</t>
+  </si>
+  <si>
+    <t>Check on JO creation Behavior</t>
+  </si>
+  <si>
+    <t>Division Head interface Page:</t>
+  </si>
+  <si>
+    <t>Remove Package Details</t>
+  </si>
+  <si>
+    <t>FP&amp;S to provide an update if email approval will flow to the tool already</t>
+  </si>
+  <si>
+    <t>Official EMAIL SUBJECT on the offer email to be sent to candidate</t>
+  </si>
+  <si>
+    <t>Landing Page per Role</t>
+  </si>
+  <si>
+    <t>Week 2</t>
+  </si>
+  <si>
+    <t>Add Notes Tab Unfer TA Partner access for approval notes from Division Head</t>
+  </si>
+  <si>
+    <t>TA interface</t>
+  </si>
+  <si>
+    <t>Change DISCUSSION NOTES to NOTES and make it not required.</t>
+  </si>
+  <si>
+    <t>PDF Attachment (for Review)</t>
+  </si>
+  <si>
+    <t>Default Benefit Index as an attachment </t>
+  </si>
+  <si>
+    <t>Change Test email button to PREVIEW</t>
+  </si>
+  <si>
+    <t>Sort Discussion Timeline Lates</t>
+  </si>
+  <si>
+    <t>Add CC TA Partner</t>
+  </si>
+  <si>
+    <t>Password protected PDF configuration for JO then to be sent to ONB.</t>
+  </si>
+  <si>
+    <t>Visible ONLY to TA Lead - HR Candidates</t>
+  </si>
+  <si>
+    <t>Visible to TA Partner - R&amp;F, AM, Confi Payroll Based on Accounts</t>
+  </si>
+  <si>
+    <t>Salary Visibility - ONB Team mask salary data candidates for HROD, AM/KP</t>
+  </si>
+  <si>
+    <t>Review content of email message in the JO option</t>
+  </si>
+  <si>
+    <t>Add TOKEN and CC to the email page</t>
+  </si>
+  <si>
+    <t>Email Page or Template  permission   = TA Partner and System Admin</t>
+  </si>
+  <si>
+    <t>Week 3</t>
+  </si>
+  <si>
+    <t>1. Setup for  Benefit Package Dependent to be sent to Candidate in PDF Format</t>
+  </si>
+  <si>
+    <t>2. Configure DB Sync Daily at night</t>
+  </si>
+  <si>
+    <t>Configure Uload file max size of 10MB</t>
+  </si>
+  <si>
+    <t>Configure Remarks section is required and must enable entry of table and image.</t>
+  </si>
+  <si>
+    <t>Division Head should be able to select a package.</t>
+  </si>
+  <si>
+    <t>Week 4</t>
+  </si>
+  <si>
+    <t>System Admin Page Configuration</t>
+  </si>
+  <si>
+    <t>Table Maintenance configuration setup (Company, Division, Roles, Salary Grade, Package) - Create, Update, Active/Inactive</t>
+  </si>
+  <si>
+    <t>New Filter for DBOX Candidates</t>
+  </si>
+  <si>
+    <t>Company Division Department and Position, remove Email Address</t>
+  </si>
+  <si>
+    <t>Last Sysn Datetime</t>
+  </si>
+  <si>
+    <t>Add Manual Sync Button</t>
+  </si>
+  <si>
+    <t>Modal import button Confirmation</t>
   </si>
 </sst>
 </file>
@@ -536,7 +669,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -567,6 +700,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -904,25 +1055,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B9038A7-AD59-482A-8671-D3CB2D87EC41}">
   <dimension ref="B2:O8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" customWidth="1"/>
-    <col min="4" max="4" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
+    <col min="4" max="4" width="34.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.21875" customWidth="1"/>
-    <col min="8" max="8" width="37.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.1796875" customWidth="1"/>
+    <col min="8" max="8" width="37.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.6328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" customWidth="1"/>
     <col min="11" max="11" width="23" customWidth="1"/>
-    <col min="12" max="12" width="20.33203125" customWidth="1"/>
-    <col min="13" max="13" width="19.44140625" customWidth="1"/>
-    <col min="14" max="14" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.36328125" customWidth="1"/>
+    <col min="13" max="13" width="19.453125" customWidth="1"/>
+    <col min="14" max="14" width="28.81640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
@@ -966,7 +1117,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1010,7 +1161,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1039,7 +1190,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1059,7 +1210,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>9</v>
       </c>
@@ -1070,12 +1221,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>49</v>
       </c>
@@ -1088,29 +1239,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED69CB7-7627-4EC8-B1DF-810A0B37AA79}">
   <dimension ref="C1:Y26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" customWidth="1"/>
-    <col min="3" max="3" width="66.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="63.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="63.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.88671875" customWidth="1"/>
-    <col min="11" max="11" width="55.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="46.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="90.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="57.21875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" customWidth="1"/>
+    <col min="3" max="3" width="66.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="63.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="63.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.90625" customWidth="1"/>
+    <col min="11" max="11" width="55.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="46.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="90.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="57.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="32.08984375" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="33" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="31.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C1" s="7">
         <v>46274</v>
       </c>
@@ -1181,7 +1332,7 @@
         <v>46296</v>
       </c>
     </row>
-    <row r="2" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1234,7 +1385,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
         <v>7</v>
       </c>
@@ -1269,7 +1420,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>8</v>
       </c>
@@ -1304,7 +1455,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>6</v>
       </c>
@@ -1342,7 +1493,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>0</v>
       </c>
@@ -1362,7 +1513,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:25" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
         <v>1</v>
       </c>
@@ -1394,7 +1545,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:25" x14ac:dyDescent="0.35">
       <c r="D8" t="s">
         <v>111</v>
       </c>
@@ -1414,7 +1565,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:25" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>155</v>
+      </c>
       <c r="D9" t="s">
         <v>112</v>
       </c>
@@ -1437,7 +1591,10 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:25" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>156</v>
+      </c>
       <c r="D10" t="s">
         <v>113</v>
       </c>
@@ -1460,7 +1617,10 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:25" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>157</v>
+      </c>
       <c r="I11" t="s">
         <v>24</v>
       </c>
@@ -1474,7 +1634,10 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:25" x14ac:dyDescent="0.35">
+      <c r="C12" t="s">
+        <v>158</v>
+      </c>
       <c r="E12" t="s">
         <v>74</v>
       </c>
@@ -1485,7 +1648,10 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:25" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>159</v>
+      </c>
       <c r="E13" t="s">
         <v>75</v>
       </c>
@@ -1496,7 +1662,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:25" x14ac:dyDescent="0.35">
       <c r="E14" s="11" t="s">
         <v>76</v>
       </c>
@@ -1504,7 +1670,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:25" x14ac:dyDescent="0.35">
       <c r="E15" s="11" t="s">
         <v>77</v>
       </c>
@@ -1512,7 +1678,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:25" x14ac:dyDescent="0.35">
       <c r="E16" s="11" t="s">
         <v>78</v>
       </c>
@@ -1523,7 +1689,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:9" x14ac:dyDescent="0.35">
       <c r="E17" s="11" t="s">
         <v>79</v>
       </c>
@@ -1531,7 +1697,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:9" x14ac:dyDescent="0.35">
       <c r="H18" t="s">
         <v>81</v>
       </c>
@@ -1539,7 +1705,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:9" x14ac:dyDescent="0.35">
       <c r="H19" s="11" t="s">
         <v>82</v>
       </c>
@@ -1547,7 +1713,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:9" x14ac:dyDescent="0.35">
       <c r="H20" s="11" t="s">
         <v>83</v>
       </c>
@@ -1555,7 +1721,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:9" x14ac:dyDescent="0.35">
       <c r="H21" s="11" t="s">
         <v>84</v>
       </c>
@@ -1563,17 +1729,17 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:9" x14ac:dyDescent="0.35">
       <c r="I23" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:9" x14ac:dyDescent="0.35">
       <c r="I24" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="26" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:9" x14ac:dyDescent="0.35">
       <c r="I26" t="s">
         <v>95</v>
       </c>
@@ -1586,52 +1752,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B8C298-1B1E-4BB2-871B-BB0A034CE40B}">
   <dimension ref="B2:B14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="123.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="123.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B2" s="14" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B3" s="15" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B4" s="15" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B5" s="14" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B6" s="12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B7" s="16" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>109</v>
       </c>
@@ -1644,4 +1810,461 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F149B5-686D-46FF-9A3A-F0C369A32F6D}">
+  <dimension ref="B2:E45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="56.08984375" customWidth="1"/>
+    <col min="3" max="3" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.1796875" customWidth="1"/>
+    <col min="5" max="5" width="9.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B2" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="20">
+        <v>46273</v>
+      </c>
+      <c r="E2" s="20">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B3" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="21">
+        <v>46274</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+    </row>
+    <row r="4" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B4" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+    </row>
+    <row r="5" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B5" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="19">
+        <v>46275</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+    </row>
+    <row r="6" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B6" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="19">
+        <v>46276</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+    </row>
+    <row r="7" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="19">
+        <v>46276</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+    </row>
+    <row r="8" spans="2:5" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="19">
+        <v>46279</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+    </row>
+    <row r="9" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B9" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="19">
+        <v>46279</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+    </row>
+    <row r="10" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B10" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="21">
+        <v>46279</v>
+      </c>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+    </row>
+    <row r="11" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B11" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="21"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+    </row>
+    <row r="12" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B12" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B13" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+    </row>
+    <row r="14" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B14" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="19">
+        <v>46279</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+    </row>
+    <row r="15" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="19">
+        <v>46279</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B16" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="19">
+        <v>46279</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B17" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="D17" s="20">
+        <v>46280</v>
+      </c>
+      <c r="E17" s="20">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B18" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="19">
+        <v>46280</v>
+      </c>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B19" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="21">
+        <v>46280</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B20" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="21"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+    </row>
+    <row r="21" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B21" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="21"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B22" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="21"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+    </row>
+    <row r="23" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B23" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="21"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+    </row>
+    <row r="24" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B24" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+    </row>
+    <row r="25" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B25" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+    </row>
+    <row r="26" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B26" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="21">
+        <v>46280</v>
+      </c>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+    </row>
+    <row r="27" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B27" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="21"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+    </row>
+    <row r="28" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B28" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" s="19">
+        <v>46280</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B29" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" s="19">
+        <v>46281</v>
+      </c>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+    </row>
+    <row r="30" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B30" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="21">
+        <v>46282</v>
+      </c>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+    </row>
+    <row r="31" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B31" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="21"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+    </row>
+    <row r="32" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B32" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" s="21"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+    </row>
+    <row r="33" spans="2:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="B33" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="19">
+        <v>46283</v>
+      </c>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+    </row>
+    <row r="34" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B34" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" s="19">
+        <v>46283</v>
+      </c>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+    </row>
+    <row r="35" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B35" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" s="19">
+        <v>46286</v>
+      </c>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+    </row>
+    <row r="36" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B36" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="19">
+        <v>46286</v>
+      </c>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B37" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" s="17"/>
+      <c r="D37" s="19">
+        <v>46287</v>
+      </c>
+      <c r="E37" s="19">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B38" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C38" s="19">
+        <v>46287</v>
+      </c>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+    </row>
+    <row r="39" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B39" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C39" s="19">
+        <v>46288</v>
+      </c>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+    </row>
+    <row r="40" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B40" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C40" s="19">
+        <v>46289</v>
+      </c>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+    </row>
+    <row r="41" spans="2:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B41" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" s="19">
+        <v>46289</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+    </row>
+    <row r="42" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B42" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" s="19">
+        <v>46290</v>
+      </c>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B43" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C43" s="17"/>
+      <c r="D43" s="20">
+        <v>46294</v>
+      </c>
+      <c r="E43" s="20">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="B44" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="19">
+        <v>46294</v>
+      </c>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+    </row>
+    <row r="45" spans="2:5" ht="87" x14ac:dyDescent="0.35">
+      <c r="B45" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="19">
+        <v>46296</v>
+      </c>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="C19:C25"/>
+    <mergeCell ref="D19:D25"/>
+    <mergeCell ref="E19:E25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="E10:E13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>